--- a/tests/IT23678804.xlsx
+++ b/tests/IT23678804.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Campus\3Y 2S\ITPM\As1\IT23678804\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97BA131A-B434-4A2C-AD12-1338DF9086EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C2D6B8-88CB-4B5E-9E7B-75A03631693F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="11625" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name=" Test cases" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="519">
   <si>
     <t>TC ID</t>
   </si>
@@ -4905,12 +4905,6 @@
     <t>Correct transliteration of core words ("Mama" to "මම", "adha" to "අද", "sathutin" to "සතුටින්"</t>
   </si>
   <si>
-    <t>Accurate handling of compound structure and past tense - Correct segmentation of words like "iye" to "ඊයේ", "polata" to "පොළට"</t>
-  </si>
-  <si>
-    <t>Minor spelling variations ("eya" to "එය", "gaththaa" to "ගත්තා") but meaning intact</t>
-  </si>
-  <si>
     <t>Input Type / Domain: Daily language usage</t>
   </si>
   <si>
@@ -4941,12 +4935,6 @@
     <t>Correct polite imperative form preserved</t>
   </si>
   <si>
-    <t>Accurate transliteration of words like "karunakarala" to "කරුණාකරලා", "issaraha" to "ඉස්සරහ"</t>
-  </si>
-  <si>
-    <t>Minor inconsistencies ("dora" to "ඩොර", "poddak" to "පොඩ්ඩක්") but overall pass</t>
-  </si>
-  <si>
     <t>Sentence / Grammar Focus: Imperative (command)</t>
   </si>
   <si>
@@ -4962,9 +4950,6 @@
     <t>Negation not handled properly ("naha" to "naha" untranslated)</t>
   </si>
   <si>
-    <t>Some words distorted ("e" to "එ", "kamata" to "කමට", "kamathi" to "කමති")</t>
-  </si>
-  <si>
     <t>Meaning partially lost</t>
   </si>
   <si>
@@ -4972,9 +4957,6 @@
   </si>
   <si>
     <t>M (31–299 characters)</t>
-  </si>
-  <si>
-    <t>Polite request form distorted ("oyata" to "ඔයට", "udau" to "උඩෞ", "puluvandha" to "පුලුවන්ද")</t>
   </si>
   <si>
     <t>Question mark preserved but spelling errors</t>
@@ -5002,12 +4984,6 @@
     <t>Imperative (command)</t>
   </si>
   <si>
-    <t>Greeting expression mostly correct but spelling errors ("Suba" to "සුබ", "Udhasanak" to "උදසනක්")</t>
-  </si>
-  <si>
-    <t>Exclamation preserved but missing "ැ"</t>
-  </si>
-  <si>
     <t>Partial failure</t>
   </si>
   <si>
@@ -5017,9 +4993,6 @@
     <t>Multi-word collection handled well</t>
   </si>
   <si>
-    <t>Minor shortenings ("Oyaata" to "ඔයට", "oyava" to "ඔයව", "balaganna" to "බලගන්න", "puluvan" to "පුලුවන්")</t>
-  </si>
-  <si>
     <t>Joined word variation segmented correctly</t>
   </si>
   <si>
@@ -5032,18 +5005,12 @@
     <t>Typographical error handling</t>
   </si>
   <si>
-    <t>Repeated emphasis partially handled ("Hari hari" correct, "eka" to "එක", "hodai" to "හොඩෛ")</t>
-  </si>
-  <si>
     <t>Spelling distortion in "hodai"</t>
   </si>
   <si>
     <t>Past tense</t>
   </si>
   <si>
-    <t>Present tense and plural distorted ("eyala" to "එයල", "dhan" to "දන්", "gahanawaa" to "ගහනwආ")</t>
-  </si>
-  <si>
     <t>English "cricket" remains, typos introduced</t>
   </si>
   <si>
@@ -5065,30 +5032,18 @@
     <t>Future tense</t>
   </si>
   <si>
-    <t>Mixed English tech terms preserved correctly ("File", "email")</t>
-  </si>
-  <si>
     <t>Imperative form accurate</t>
   </si>
   <si>
     <t>Mixed Singlish + English</t>
   </si>
   <si>
-    <t>Place name "galle" not transliterated, remains English</t>
-  </si>
-  <si>
     <t>Verb correct but overall failure due to untranslated proper noun</t>
   </si>
   <si>
     <t>Names / places / common English words</t>
   </si>
   <si>
-    <t>Abbreviation "NIC" preserved</t>
-  </si>
-  <si>
-    <t>Possessive and command form mostly correct ("Oyaage" to "ඔයාගෙ")</t>
-  </si>
-  <si>
     <t>Punctuation "?" preserved but entire output remains Singlish</t>
   </si>
   <si>
@@ -5107,12 +5062,6 @@
     <t>Currency "Rs. 1000" preserved correctly</t>
   </si>
   <si>
-    <t>Structure intact with minor variations ("ekee" to "එකේ")</t>
-  </si>
-  <si>
-    <t>Time "10AM" preserved</t>
-  </si>
-  <si>
     <t>English "meeting" remains</t>
   </si>
   <si>
@@ -5122,9 +5071,6 @@
     <t>Structure correct</t>
   </si>
   <si>
-    <t>Multiple spaces handled but output has errors ("Hello" to "Hello", "yaluvaa" to "යලුවා", "Suba udhaasanak" to "සුබ උදාසනක්", "Oyata" to "ඔයට")</t>
-  </si>
-  <si>
     <t>Greetings distorted</t>
   </si>
   <si>
@@ -5153,12 +5099,6 @@
   </si>
   <si>
     <t>Robustness validation</t>
-  </si>
-  <si>
-    <t>Joined words partially handled but errors ("monwahri" to "මොන්වාහ්‍රි", "ikmanta" to "ඉක්මන්ට", "ganna one" to "ගන්න one")</t>
-  </si>
-  <si>
-    <t>English "shoping" to "ශොපින්ග්"</t>
   </si>
   <si>
     <t>Robust but not perfect, marked Pass (adjust to Fail for issues)</t>
@@ -5180,9 +5120,6 @@
     <t>Pass marked but issues suggest Fail</t>
   </si>
   <si>
-    <t>Heavy mixed English ("instergram", "snapchat", "use") partially transliterated but errors ("or" remains, "karanne na" to "කරන්නේ න", "thawath" to "තwඅත්")</t>
-  </si>
-  <si>
     <t>Negative form distorted</t>
   </si>
   <si>
@@ -5204,25 +5141,16 @@
     <t>Exclamation intact</t>
   </si>
   <si>
-    <t>Mixed abbreviations ("pdf", "otp", "ASAP") remain English, distortions ("kara" to "කර", "balann" to "බලන්න්")</t>
-  </si>
-  <si>
     <t>Complex sentence fails robustness</t>
   </si>
   <si>
     <t>Pass marked but adjust to Fail</t>
   </si>
   <si>
-    <t>Fast-typed joined words break output ("wahama" to "wඅහම", "ewann" to "එwඅන්න්", "urgent" remains)</t>
-  </si>
-  <si>
     <t>Politeness lost</t>
   </si>
   <si>
     <t>Failure</t>
-  </si>
-  <si>
-    <t>Slang heavy ("Machan", "da", "full hype hoo") distorted ("party da" to "party ඩ", "hype hoo" to "hype හෝ")</t>
   </si>
   <si>
     <t>Question form partial</t>
@@ -5475,13 +5403,88 @@
   </si>
   <si>
     <t xml:space="preserve">Mama rata yanna hadanava saha oya ada envadha? </t>
+  </si>
+  <si>
+    <t>fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor spelling variations </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accurate handling of compound structure and past tense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor inconsistencies </t>
+  </si>
+  <si>
+    <t>Accurate transliteration</t>
+  </si>
+  <si>
+    <t>Input Length Type: s (30&gt;text)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some words distorted </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polite request form distorted </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greeting expression mostly correct but spelling errors </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exclamation preserved but missing </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor shortenings </t>
+  </si>
+  <si>
+    <t>Repeated emphasis partially handled</t>
+  </si>
+  <si>
+    <t>Present tense and plural distorted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed English tech terms preserved correctly </t>
+  </si>
+  <si>
+    <t>Place name "Matale" not transliterated, remains English</t>
+  </si>
+  <si>
+    <t>Abbreviation "Student" preserved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possessive and command form mostly correct </t>
+  </si>
+  <si>
+    <t>Structure intact with minor variations</t>
+  </si>
+  <si>
+    <t>Time "5AM" preserved</t>
+  </si>
+  <si>
+    <t>Multiple spaces handled but output has errors</t>
+  </si>
+  <si>
+    <t>Joined words partially handled but errors</t>
+  </si>
+  <si>
+    <t>Heavy mixed English ("Social", "use", "krnne") partially transliterated but errors</t>
+  </si>
+  <si>
+    <t>Mixed abbreviationsremain English, distortions (</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fast-typed joined words break output </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slang heavy </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5795,29 +5798,26 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5828,9 +5828,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -5840,13 +5837,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6130,7 +6133,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I141"/>
-  <sheetFormatPr defaultRowHeight="49.9" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="49.9" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="9.28515625" customWidth="1"/>
@@ -6144,7 +6147,7 @@
     <col min="12" max="13" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="36.6" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6173,26 +6176,28 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+    <row r="2" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A2" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="22" t="s">
         <v>232</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D2" s="28" t="s">
-        <v>463</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>465</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>464</v>
-      </c>
-      <c r="G2" s="27"/>
+      <c r="D2" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>440</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>315</v>
+      </c>
       <c r="H2" s="18" t="s">
         <v>322</v>
       </c>
@@ -6200,14 +6205,14 @@
         <v>324</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="27"/>
+    <row r="3" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A3" s="23"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="22"/>
       <c r="H3" s="19" t="s">
         <v>328</v>
       </c>
@@ -6215,14 +6220,14 @@
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="27"/>
+    <row r="4" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A4" s="23"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="22"/>
       <c r="H4" s="18" t="s">
         <v>323</v>
       </c>
@@ -6230,2431 +6235,2624 @@
         <v>326</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="27"/>
+    <row r="5" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A5" s="23"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="22"/>
       <c r="H5" s="18"/>
       <c r="I5" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="33" t="s">
+    <row r="6" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A6" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>445</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>446</v>
-      </c>
-      <c r="F6" s="37" t="s">
-        <v>446</v>
-      </c>
-      <c r="G6" s="27"/>
+      <c r="D6" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>422</v>
+      </c>
+      <c r="F6" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>315</v>
+      </c>
       <c r="H6" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="I6" s="21" t="s">
         <v>329</v>
       </c>
-      <c r="I6" s="21" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="27"/>
+    </row>
+    <row r="7" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="22"/>
       <c r="H7" s="21" t="s">
+        <v>495</v>
+      </c>
+      <c r="I7" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="I7" s="21" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="27"/>
+    </row>
+    <row r="8" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="22"/>
       <c r="H8" s="21"/>
       <c r="I8" s="21" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="27"/>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="22"/>
       <c r="H9" s="21"/>
       <c r="I9" s="21" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A10" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="D10" s="34" t="s">
-        <v>447</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>448</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>449</v>
-      </c>
-      <c r="G10" s="27"/>
+      <c r="D10" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>424</v>
+      </c>
+      <c r="F10" s="29" t="s">
+        <v>425</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>494</v>
+      </c>
       <c r="H10" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A11" s="23"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="18" t="s">
+        <v>498</v>
+      </c>
+      <c r="I11" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="I10" s="18" t="s">
+    </row>
+    <row r="12" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A12" s="23"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="18" t="s">
+        <v>497</v>
+      </c>
+      <c r="I12" s="18" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="33"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="33"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="27"/>
+    <row r="13" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A13" s="23"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="22"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A14" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>427</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>450</v>
-      </c>
-      <c r="D14" s="28" t="s">
+      <c r="I14" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="E14" s="29" t="s">
-        <v>451</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="I14" s="18" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="18" t="s">
-        <v>341</v>
-      </c>
+    </row>
+    <row r="15" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A15" s="24"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="18"/>
       <c r="I15" s="18" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="18" t="s">
-        <v>342</v>
-      </c>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A16" s="24"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="18"/>
       <c r="I16" s="18" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="27"/>
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A17" s="24"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="22"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A18" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>452</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>453</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>454</v>
-      </c>
-      <c r="G18" s="24"/>
+      <c r="D18" s="37" t="s">
+        <v>428</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>429</v>
+      </c>
+      <c r="F18" s="37" t="s">
+        <v>430</v>
+      </c>
+      <c r="G18" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H18" s="18" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="24"/>
+    <row r="19" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A19" s="35"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="35"/>
       <c r="H19" s="18" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="24"/>
+    <row r="20" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A20" s="35"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="18" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="24"/>
+    <row r="21" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A21" s="35"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="35"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
+    <row r="22" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A22" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>456</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>457</v>
-      </c>
-      <c r="G22" s="24"/>
+      <c r="D22" s="35" t="s">
+        <v>431</v>
+      </c>
+      <c r="E22" s="36" t="s">
+        <v>432</v>
+      </c>
+      <c r="F22" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H22" s="18" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="24"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="24"/>
+    <row r="23" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A23" s="35"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="35"/>
       <c r="H23" s="18" t="s">
-        <v>348</v>
+        <v>500</v>
       </c>
       <c r="I23" s="18" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="24"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="26"/>
-      <c r="G24" s="24"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A24" s="35"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="35"/>
       <c r="H24" s="18" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="I24" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A25" s="35"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="35"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+    <row r="26" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A26" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D26" s="24" t="s">
-        <v>458</v>
-      </c>
-      <c r="E26" s="25" t="s">
-        <v>459</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>459</v>
-      </c>
-      <c r="G26" s="24" t="s">
+      <c r="D26" s="35" t="s">
+        <v>434</v>
+      </c>
+      <c r="E26" s="36" t="s">
+        <v>435</v>
+      </c>
+      <c r="F26" s="37" t="s">
+        <v>435</v>
+      </c>
+      <c r="G26" s="35" t="s">
         <v>315</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>352</v>
+        <v>501</v>
       </c>
       <c r="I26" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="26"/>
-      <c r="G27" s="24"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A27" s="35"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="35"/>
       <c r="H27" s="18" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="I27" s="18" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="24"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A28" s="35"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="35"/>
       <c r="H28" s="18" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="I28" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="24"/>
+    <row r="29" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A29" s="35"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="18"/>
       <c r="I29" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
+    <row r="30" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A30" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D30" s="24" t="s">
-        <v>460</v>
-      </c>
-      <c r="E30" s="24" t="s">
-        <v>462</v>
-      </c>
-      <c r="F30" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="G30" s="24" t="s">
-        <v>315</v>
+      <c r="D30" s="35" t="s">
+        <v>436</v>
+      </c>
+      <c r="E30" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="F30" s="37" t="s">
+        <v>437</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>494</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="I30" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="26"/>
-      <c r="G31" s="24"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A31" s="35"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="18" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="I31" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
-      <c r="F32" s="26"/>
-      <c r="G32" s="24"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A32" s="35"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="18"/>
       <c r="I32" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A33" s="35"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="18"/>
       <c r="I33" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="24" t="s">
+    <row r="34" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A34" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="B34" s="24" t="s">
+      <c r="B34" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="C34" s="24" t="s">
+      <c r="C34" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D34" s="24" t="s">
-        <v>443</v>
-      </c>
-      <c r="E34" s="25" t="s">
-        <v>444</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>444</v>
-      </c>
-      <c r="G34" s="24"/>
+      <c r="D34" s="35" t="s">
+        <v>419</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>420</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>420</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H34" s="18" t="s">
-        <v>361</v>
+        <v>502</v>
       </c>
       <c r="I34" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="24"/>
-      <c r="B35" s="24"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="24"/>
+        <v>349</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A35" s="35"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="18" t="s">
-        <v>362</v>
+        <v>503</v>
       </c>
       <c r="I35" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24"/>
-      <c r="B36" s="24"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="24"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="24"/>
+    <row r="36" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A36" s="35"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="38"/>
+      <c r="G36" s="35"/>
       <c r="H36" s="18" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="I36" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="24"/>
+    <row r="37" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A37" s="35"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="35"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
+    <row r="38" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A38" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="D38" s="24" t="s">
-        <v>466</v>
-      </c>
-      <c r="E38" s="25" t="s">
-        <v>468</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>467</v>
-      </c>
-      <c r="G38" s="24"/>
+      <c r="D38" s="35" t="s">
+        <v>442</v>
+      </c>
+      <c r="E38" s="36" t="s">
+        <v>444</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H38" s="18" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="I38" s="18" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="24"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A39" s="35"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="38"/>
+      <c r="G39" s="35"/>
       <c r="H39" s="18" t="s">
-        <v>366</v>
+        <v>504</v>
       </c>
       <c r="I39" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="26"/>
-      <c r="G40" s="24"/>
+    <row r="40" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A40" s="35"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="35"/>
       <c r="H40" s="18" t="s">
         <v>322</v>
       </c>
       <c r="I40" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="39"/>
+      <c r="G41" s="35"/>
       <c r="H41" s="18"/>
       <c r="I41" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="24" t="s">
+    <row r="42" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A42" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D42" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="E42" s="25" t="s">
-        <v>470</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>470</v>
-      </c>
-      <c r="G42" s="24"/>
+      <c r="D42" s="35" t="s">
+        <v>445</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>446</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H42" s="18" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="I42" s="18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="24"/>
-      <c r="D43" s="24"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="26"/>
-      <c r="G43" s="24"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A43" s="35"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="35"/>
       <c r="H43" s="18" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I43" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="24"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="26"/>
-      <c r="G44" s="24"/>
+    <row r="44" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A44" s="35"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="35"/>
       <c r="H44" s="18" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="I44" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
+    <row r="45" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A45" s="35"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="39"/>
+      <c r="G45" s="35"/>
       <c r="H45" s="18"/>
       <c r="I45" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="24" t="s">
+    <row r="46" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A46" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D46" s="24" t="s">
-        <v>471</v>
-      </c>
-      <c r="E46" s="25" t="s">
-        <v>472</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>472</v>
-      </c>
-      <c r="G46" s="24"/>
+      <c r="D46" s="35" t="s">
+        <v>447</v>
+      </c>
+      <c r="E46" s="36" t="s">
+        <v>448</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>448</v>
+      </c>
+      <c r="G46" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H46" s="18" t="s">
-        <v>371</v>
+        <v>505</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="25"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="24"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A47" s="35"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="35"/>
       <c r="H47" s="18" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="I47" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="26"/>
-      <c r="G48" s="24"/>
+    <row r="48" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A48" s="35"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="35"/>
       <c r="H48" s="18" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="I48" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="24"/>
-      <c r="B49" s="24"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A49" s="35"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="35"/>
       <c r="H49" s="18"/>
       <c r="I49" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="24" t="s">
+    <row r="50" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A50" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="C50" s="24" t="s">
+      <c r="C50" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D50" s="24" t="s">
-        <v>473</v>
-      </c>
-      <c r="E50" s="25" t="s">
-        <v>475</v>
-      </c>
-      <c r="F50" s="25" t="s">
-        <v>474</v>
-      </c>
-      <c r="G50" s="22"/>
+      <c r="D50" s="35" t="s">
+        <v>449</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>451</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>450</v>
+      </c>
+      <c r="G50" s="37" t="s">
+        <v>315</v>
+      </c>
       <c r="H50" s="18" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I50" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="24"/>
-      <c r="B51" s="24"/>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="26"/>
+    <row r="51" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A51" s="35"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="38"/>
       <c r="H51" s="18"/>
       <c r="I51" s="18" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="26"/>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A52" s="35"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="38"/>
       <c r="H52" s="18"/>
       <c r="I52" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="23"/>
+    <row r="53" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A53" s="35"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="39"/>
       <c r="H53" s="18"/>
       <c r="I53" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="24" t="s">
+    <row r="54" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A54" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D54" s="24" t="s">
-        <v>476</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>477</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>478</v>
-      </c>
-      <c r="G54" s="24"/>
+      <c r="D54" s="35" t="s">
+        <v>452</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="F54" s="37" t="s">
+        <v>454</v>
+      </c>
+      <c r="G54" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H54" s="18" t="s">
-        <v>374</v>
+        <v>506</v>
       </c>
       <c r="I54" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="24"/>
-      <c r="B55" s="24"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="25"/>
-      <c r="F55" s="26"/>
-      <c r="G55" s="24"/>
+    <row r="55" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A55" s="35"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="38"/>
+      <c r="G55" s="35"/>
       <c r="H55" s="18" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="I55" s="18" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="24"/>
-      <c r="B56" s="24"/>
-      <c r="C56" s="24"/>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25"/>
-      <c r="F56" s="26"/>
-      <c r="G56" s="24"/>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="36"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="35"/>
       <c r="H56" s="18" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I56" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="24"/>
-      <c r="B57" s="24"/>
-      <c r="C57" s="24"/>
-      <c r="D57" s="24"/>
-      <c r="E57" s="25"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A57" s="35"/>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="36"/>
+      <c r="F57" s="39"/>
+      <c r="G57" s="35"/>
       <c r="H57" s="18"/>
       <c r="I57" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="24" t="s">
+    <row r="58" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A58" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="B58" s="24" t="s">
+      <c r="B58" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D58" s="24" t="s">
-        <v>479</v>
-      </c>
-      <c r="E58" s="25" t="s">
-        <v>480</v>
-      </c>
-      <c r="F58" s="22" t="s">
-        <v>480</v>
-      </c>
-      <c r="G58" s="24"/>
+      <c r="D58" s="35" t="s">
+        <v>455</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="F58" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="G58" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H58" s="18" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="I58" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="25"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="24"/>
+    <row r="59" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A59" s="35"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="35"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="36"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="35"/>
       <c r="H59" s="18" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="I59" s="18" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="25"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="24"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A60" s="35"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="35"/>
+      <c r="D60" s="35"/>
+      <c r="E60" s="36"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="35"/>
       <c r="H60" s="18" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="I60" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="24"/>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="24"/>
+    <row r="61" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A61" s="35"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="35"/>
+      <c r="D61" s="35"/>
+      <c r="E61" s="36"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="35"/>
       <c r="H61" s="18"/>
       <c r="I61" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="24" t="s">
+    <row r="62" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A62" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D62" s="24" t="s">
-        <v>481</v>
-      </c>
-      <c r="E62" s="25" t="s">
-        <v>482</v>
-      </c>
-      <c r="F62" s="22" t="s">
-        <v>482</v>
-      </c>
-      <c r="G62" s="24"/>
+      <c r="D62" s="35" t="s">
+        <v>457</v>
+      </c>
+      <c r="E62" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="F62" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="G62" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H62" s="18" t="s">
-        <v>382</v>
+        <v>507</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="24"/>
-      <c r="B63" s="24"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="24"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="24"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A63" s="35"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="35"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="36"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="35"/>
       <c r="H63" s="18" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="24"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A64" s="35"/>
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="36"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="35"/>
       <c r="H64" s="18" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="23"/>
-      <c r="G65" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A65" s="35"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="36"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="35"/>
       <c r="H65" s="18"/>
       <c r="I65" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="24" t="s">
+    <row r="66" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A66" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D66" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="E66" s="25" t="s">
-        <v>485</v>
-      </c>
-      <c r="F66" s="22" t="s">
-        <v>484</v>
-      </c>
-      <c r="G66" s="24"/>
+      <c r="D66" s="35" t="s">
+        <v>459</v>
+      </c>
+      <c r="E66" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>460</v>
+      </c>
+      <c r="G66" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H66" s="18" t="s">
-        <v>385</v>
+        <v>508</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="24"/>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A67" s="35"/>
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="35"/>
+      <c r="E67" s="36"/>
+      <c r="F67" s="38"/>
+      <c r="G67" s="35"/>
       <c r="H67" s="18" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="I67" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="24"/>
-      <c r="B68" s="24"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="24"/>
-      <c r="E68" s="25"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="24"/>
+    <row r="68" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A68" s="35"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="36"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="35"/>
       <c r="H68" s="18"/>
       <c r="I68" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="24"/>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="25"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="24"/>
+    <row r="69" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A69" s="35"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="35"/>
+      <c r="D69" s="35"/>
+      <c r="E69" s="36"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="35"/>
       <c r="H69" s="18"/>
       <c r="I69" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="24" t="s">
+    <row r="70" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A70" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D70" s="24" t="s">
-        <v>486</v>
-      </c>
-      <c r="E70" s="25" t="s">
-        <v>488</v>
-      </c>
-      <c r="F70" s="22" t="s">
-        <v>487</v>
-      </c>
-      <c r="G70" s="24"/>
+      <c r="D70" s="35" t="s">
+        <v>462</v>
+      </c>
+      <c r="E70" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="F70" s="37" t="s">
+        <v>463</v>
+      </c>
+      <c r="G70" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H70" s="18" t="s">
-        <v>388</v>
+        <v>509</v>
       </c>
       <c r="I70" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="24"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A71" s="35"/>
+      <c r="B71" s="35"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="38"/>
+      <c r="G71" s="35"/>
       <c r="H71" s="18" t="s">
-        <v>389</v>
+        <v>510</v>
       </c>
       <c r="I71" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="72" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="26"/>
-      <c r="G72" s="24"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A72" s="35"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="38"/>
+      <c r="G72" s="35"/>
       <c r="H72" s="18" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="I72" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="25"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A73" s="35"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="36"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="35"/>
       <c r="H73" s="18"/>
       <c r="I73" s="18" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="24" t="s">
+    <row r="74" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A74" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="C74" s="24" t="s">
+      <c r="C74" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D74" s="24" t="s">
-        <v>489</v>
-      </c>
-      <c r="E74" s="25" t="s">
-        <v>490</v>
-      </c>
-      <c r="F74" s="22" t="s">
-        <v>491</v>
-      </c>
-      <c r="G74" s="24"/>
+      <c r="D74" s="35" t="s">
+        <v>465</v>
+      </c>
+      <c r="E74" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="F74" s="37" t="s">
+        <v>467</v>
+      </c>
+      <c r="G74" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H74" s="18" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="I74" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="25"/>
-      <c r="F75" s="26"/>
-      <c r="G75" s="24"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A75" s="35"/>
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="36"/>
+      <c r="F75" s="38"/>
+      <c r="G75" s="35"/>
       <c r="H75" s="18" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="I75" s="18" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="24"/>
-      <c r="B76" s="24"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="24"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="26"/>
-      <c r="G76" s="24"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A76" s="35"/>
+      <c r="B76" s="35"/>
+      <c r="C76" s="35"/>
+      <c r="D76" s="35"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="38"/>
+      <c r="G76" s="35"/>
       <c r="H76" s="18" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="I76" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="24"/>
-      <c r="B77" s="24"/>
-      <c r="C77" s="24"/>
-      <c r="D77" s="24"/>
-      <c r="E77" s="25"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="24"/>
+    <row r="77" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A77" s="35"/>
+      <c r="B77" s="35"/>
+      <c r="C77" s="35"/>
+      <c r="D77" s="35"/>
+      <c r="E77" s="36"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="35"/>
       <c r="H77" s="18"/>
       <c r="I77" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A78" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D78" s="24" t="s">
-        <v>492</v>
-      </c>
-      <c r="E78" s="25" t="s">
-        <v>493</v>
-      </c>
-      <c r="F78" s="22" t="s">
+      <c r="D78" s="35" t="s">
+        <v>468</v>
+      </c>
+      <c r="E78" s="36" t="s">
+        <v>469</v>
+      </c>
+      <c r="F78" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="G78" s="35" t="s">
         <v>494</v>
       </c>
-      <c r="G78" s="24"/>
       <c r="H78" s="18" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="I78" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="24"/>
-      <c r="B79" s="24"/>
-      <c r="C79" s="24"/>
-      <c r="D79" s="24"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="24"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A79" s="35"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="35"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="35"/>
       <c r="H79" s="18" t="s">
-        <v>396</v>
+        <v>511</v>
       </c>
       <c r="I79" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
-      <c r="B80" s="24"/>
-      <c r="C80" s="24"/>
-      <c r="D80" s="24"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="26"/>
-      <c r="G80" s="24"/>
+    <row r="80" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A80" s="35"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="35"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="35"/>
       <c r="H80" s="18"/>
       <c r="I80" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="24"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A81" s="35"/>
+      <c r="B81" s="35"/>
+      <c r="C81" s="35"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="39"/>
+      <c r="G81" s="35"/>
       <c r="H81" s="18"/>
       <c r="I81" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A82" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D82" s="24" t="s">
-        <v>495</v>
-      </c>
-      <c r="E82" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="F82" s="22" t="s">
-        <v>496</v>
-      </c>
-      <c r="G82" s="24"/>
+      <c r="D82" s="35" t="s">
+        <v>471</v>
+      </c>
+      <c r="E82" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="F82" s="37" t="s">
+        <v>472</v>
+      </c>
+      <c r="G82" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H82" s="18" t="s">
-        <v>397</v>
+        <v>512</v>
       </c>
       <c r="I82" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="24"/>
-      <c r="B83" s="24"/>
-      <c r="C83" s="24"/>
-      <c r="D83" s="24"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="26"/>
-      <c r="G83" s="24"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A83" s="35"/>
+      <c r="B83" s="35"/>
+      <c r="C83" s="35"/>
+      <c r="D83" s="35"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="38"/>
+      <c r="G83" s="35"/>
       <c r="H83" s="18" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="I83" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="24"/>
-      <c r="B84" s="24"/>
-      <c r="C84" s="24"/>
-      <c r="D84" s="24"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="26"/>
-      <c r="G84" s="24"/>
+    <row r="84" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A84" s="35"/>
+      <c r="B84" s="35"/>
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="38"/>
+      <c r="G84" s="35"/>
       <c r="H84" s="18" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="I84" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="24"/>
-      <c r="B85" s="24"/>
-      <c r="C85" s="24"/>
-      <c r="D85" s="24"/>
-      <c r="E85" s="25"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="24"/>
+    <row r="85" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A85" s="35"/>
+      <c r="B85" s="35"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="36"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="35"/>
       <c r="H85" s="18"/>
       <c r="I85" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A86" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B86" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="C86" s="24" t="s">
+      <c r="C86" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D86" s="24" t="s">
-        <v>497</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>499</v>
-      </c>
-      <c r="F86" s="24" t="s">
-        <v>498</v>
-      </c>
-      <c r="G86" s="24"/>
+      <c r="D86" s="35" t="s">
+        <v>473</v>
+      </c>
+      <c r="E86" s="36" t="s">
+        <v>475</v>
+      </c>
+      <c r="F86" s="35" t="s">
+        <v>474</v>
+      </c>
+      <c r="G86" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H86" s="18" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="I86" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="24"/>
-      <c r="B87" s="24"/>
-      <c r="C87" s="24"/>
-      <c r="D87" s="24"/>
-      <c r="E87" s="25"/>
-      <c r="F87" s="24"/>
-      <c r="G87" s="24"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A87" s="35"/>
+      <c r="B87" s="35"/>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
       <c r="H87" s="18" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="I87" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="24"/>
-      <c r="B88" s="24"/>
-      <c r="C88" s="24"/>
-      <c r="D88" s="24"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="24"/>
-      <c r="G88" s="24"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A88" s="35"/>
+      <c r="B88" s="35"/>
+      <c r="C88" s="35"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
       <c r="H88" s="18"/>
       <c r="I88" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="24"/>
-      <c r="B89" s="24"/>
-      <c r="C89" s="24"/>
-      <c r="D89" s="24"/>
-      <c r="E89" s="25"/>
-      <c r="F89" s="24"/>
-      <c r="G89" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A89" s="35"/>
+      <c r="B89" s="35"/>
+      <c r="C89" s="35"/>
+      <c r="D89" s="35"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="35"/>
+      <c r="G89" s="35"/>
       <c r="H89" s="18"/>
       <c r="I89" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A90" s="35" t="s">
         <v>271</v>
       </c>
-      <c r="B90" s="24" t="s">
+      <c r="B90" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D90" s="24" t="s">
-        <v>500</v>
-      </c>
-      <c r="E90" s="25" t="s">
-        <v>501</v>
-      </c>
-      <c r="F90" s="24" t="s">
-        <v>501</v>
-      </c>
-      <c r="G90" s="24"/>
+      <c r="D90" s="35" t="s">
+        <v>476</v>
+      </c>
+      <c r="E90" s="36" t="s">
+        <v>477</v>
+      </c>
+      <c r="F90" s="35" t="s">
+        <v>477</v>
+      </c>
+      <c r="G90" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H90" s="18" t="s">
-        <v>401</v>
+        <v>513</v>
       </c>
       <c r="I90" s="18" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="24"/>
-      <c r="B91" s="24"/>
-      <c r="C91" s="24"/>
-      <c r="D91" s="24"/>
-      <c r="E91" s="25"/>
-      <c r="F91" s="24"/>
-      <c r="G91" s="24"/>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A91" s="35"/>
+      <c r="B91" s="35"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="36"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
       <c r="H91" s="18" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="I91" s="18" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="24"/>
-      <c r="C92" s="24"/>
-      <c r="D92" s="24"/>
-      <c r="E92" s="25"/>
-      <c r="F92" s="24"/>
-      <c r="G92" s="24"/>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A92" s="35"/>
+      <c r="B92" s="35"/>
+      <c r="C92" s="35"/>
+      <c r="D92" s="35"/>
+      <c r="E92" s="36"/>
+      <c r="F92" s="35"/>
+      <c r="G92" s="35"/>
       <c r="H92" s="18" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="I92" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="24"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="24"/>
-      <c r="D93" s="24"/>
-      <c r="E93" s="25"/>
-      <c r="F93" s="24"/>
-      <c r="G93" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A93" s="35"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="36"/>
+      <c r="F93" s="35"/>
+      <c r="G93" s="35"/>
       <c r="H93" s="18"/>
       <c r="I93" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A94" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="B94" s="24" t="s">
+      <c r="B94" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="D94" s="24" t="s">
-        <v>502</v>
-      </c>
-      <c r="E94" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="F94" s="24" t="s">
-        <v>504</v>
-      </c>
-      <c r="G94" s="24"/>
+      <c r="D94" s="35" t="s">
+        <v>478</v>
+      </c>
+      <c r="E94" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="F94" s="35" t="s">
+        <v>480</v>
+      </c>
+      <c r="G94" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H94" s="18" t="s">
-        <v>406</v>
+        <v>388</v>
       </c>
       <c r="I94" s="18" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
-      <c r="B95" s="24"/>
-      <c r="C95" s="24"/>
-      <c r="D95" s="24"/>
-      <c r="E95" s="25"/>
-      <c r="F95" s="24"/>
-      <c r="G95" s="24"/>
+        <v>390</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A95" s="35"/>
+      <c r="B95" s="35"/>
+      <c r="C95" s="35"/>
+      <c r="D95" s="35"/>
+      <c r="E95" s="36"/>
+      <c r="F95" s="35"/>
+      <c r="G95" s="35"/>
       <c r="H95" s="18" t="s">
-        <v>407</v>
+        <v>389</v>
       </c>
       <c r="I95" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="24"/>
-      <c r="B96" s="24"/>
-      <c r="C96" s="24"/>
-      <c r="D96" s="24"/>
-      <c r="E96" s="25"/>
-      <c r="F96" s="24"/>
-      <c r="G96" s="24"/>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A96" s="35"/>
+      <c r="B96" s="35"/>
+      <c r="C96" s="35"/>
+      <c r="D96" s="35"/>
+      <c r="E96" s="36"/>
+      <c r="F96" s="35"/>
+      <c r="G96" s="35"/>
       <c r="H96" s="18" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="I96" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="24"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="24"/>
-      <c r="D97" s="24"/>
-      <c r="E97" s="25"/>
-      <c r="F97" s="24"/>
-      <c r="G97" s="24"/>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A97" s="35"/>
+      <c r="B97" s="35"/>
+      <c r="C97" s="35"/>
+      <c r="D97" s="35"/>
+      <c r="E97" s="36"/>
+      <c r="F97" s="35"/>
+      <c r="G97" s="35"/>
       <c r="H97" s="18"/>
       <c r="I97" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A98" s="35" t="s">
         <v>283</v>
       </c>
-      <c r="B98" s="24" t="s">
+      <c r="B98" s="35" t="s">
         <v>301</v>
       </c>
-      <c r="C98" s="24" t="s">
+      <c r="C98" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D98" s="24" t="s">
-        <v>505</v>
-      </c>
-      <c r="E98" s="25" t="s">
-        <v>507</v>
-      </c>
-      <c r="F98" s="22" t="s">
-        <v>506</v>
-      </c>
-      <c r="G98" s="24"/>
+      <c r="D98" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="E98" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="F98" s="37" t="s">
+        <v>482</v>
+      </c>
+      <c r="G98" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H98" s="18" t="s">
-        <v>412</v>
+        <v>514</v>
       </c>
       <c r="I98" s="18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="24"/>
-      <c r="D99" s="24"/>
-      <c r="E99" s="25"/>
-      <c r="F99" s="26"/>
-      <c r="G99" s="24"/>
-      <c r="H99" s="18" t="s">
-        <v>413</v>
-      </c>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A99" s="35"/>
+      <c r="B99" s="35"/>
+      <c r="C99" s="35"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="36"/>
+      <c r="F99" s="38"/>
+      <c r="G99" s="35"/>
+      <c r="H99" s="18"/>
       <c r="I99" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="24"/>
-      <c r="B100" s="24"/>
-      <c r="C100" s="24"/>
-      <c r="D100" s="24"/>
-      <c r="E100" s="25"/>
-      <c r="F100" s="26"/>
-      <c r="G100" s="24"/>
+    <row r="100" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A100" s="35"/>
+      <c r="B100" s="35"/>
+      <c r="C100" s="35"/>
+      <c r="D100" s="35"/>
+      <c r="E100" s="36"/>
+      <c r="F100" s="38"/>
+      <c r="G100" s="35"/>
       <c r="H100" s="18" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="I100" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="24"/>
-      <c r="B101" s="24"/>
-      <c r="C101" s="24"/>
-      <c r="D101" s="24"/>
-      <c r="E101" s="25"/>
-      <c r="F101" s="23"/>
-      <c r="G101" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A101" s="35"/>
+      <c r="B101" s="35"/>
+      <c r="C101" s="35"/>
+      <c r="D101" s="35"/>
+      <c r="E101" s="36"/>
+      <c r="F101" s="39"/>
+      <c r="G101" s="35"/>
       <c r="H101" s="18"/>
       <c r="I101" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A102" s="35" t="s">
         <v>284</v>
       </c>
-      <c r="B102" s="24" t="s">
+      <c r="B102" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="C102" s="24" t="s">
+      <c r="C102" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D102" s="24" t="s">
+      <c r="D102" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="E102" s="25" t="s">
+      <c r="E102" s="36" t="s">
         <v>294</v>
       </c>
-      <c r="F102" s="24" t="s">
+      <c r="F102" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="G102" s="24"/>
+      <c r="G102" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H102" s="18" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="I102" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="24"/>
-      <c r="B103" s="24"/>
-      <c r="C103" s="24"/>
-      <c r="D103" s="24"/>
-      <c r="E103" s="25"/>
-      <c r="F103" s="24"/>
-      <c r="G103" s="24"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A103" s="35"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="35"/>
+      <c r="E103" s="36"/>
+      <c r="F103" s="35"/>
+      <c r="G103" s="35"/>
       <c r="H103" s="18" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="I103" s="18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="24"/>
-      <c r="B104" s="24"/>
-      <c r="C104" s="24"/>
-      <c r="D104" s="24"/>
-      <c r="E104" s="25"/>
-      <c r="F104" s="24"/>
-      <c r="G104" s="24"/>
+        <v>354</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A104" s="35"/>
+      <c r="B104" s="35"/>
+      <c r="C104" s="35"/>
+      <c r="D104" s="35"/>
+      <c r="E104" s="36"/>
+      <c r="F104" s="35"/>
+      <c r="G104" s="35"/>
       <c r="H104" s="18" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="I104" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="24"/>
-      <c r="B105" s="24"/>
-      <c r="C105" s="24"/>
-      <c r="D105" s="24"/>
-      <c r="E105" s="25"/>
-      <c r="F105" s="24"/>
-      <c r="G105" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A105" s="35"/>
+      <c r="B105" s="35"/>
+      <c r="C105" s="35"/>
+      <c r="D105" s="35"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="35"/>
+      <c r="G105" s="35"/>
       <c r="H105" s="18"/>
       <c r="I105" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A106" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="B106" s="35" t="s">
         <v>295</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="D106" s="24" t="s">
+      <c r="D106" s="35" t="s">
         <v>296</v>
       </c>
-      <c r="E106" s="25" t="s">
+      <c r="E106" s="36" t="s">
         <v>297</v>
       </c>
-      <c r="F106" s="22" t="s">
+      <c r="F106" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="G106" s="24"/>
-      <c r="H106" s="22" t="s">
-        <v>418</v>
+      <c r="G106" s="35" t="s">
+        <v>494</v>
+      </c>
+      <c r="H106" s="37" t="s">
+        <v>398</v>
       </c>
       <c r="I106" s="18" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="24"/>
-      <c r="B107" s="24"/>
-      <c r="C107" s="24"/>
-      <c r="D107" s="24"/>
-      <c r="E107" s="25"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="24"/>
-      <c r="H107" s="23"/>
+        <v>386</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A107" s="35"/>
+      <c r="B107" s="35"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="35"/>
+      <c r="E107" s="36"/>
+      <c r="F107" s="38"/>
+      <c r="G107" s="35"/>
+      <c r="H107" s="39"/>
       <c r="I107" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="24"/>
-      <c r="B108" s="24"/>
-      <c r="C108" s="24"/>
-      <c r="D108" s="24"/>
-      <c r="E108" s="25"/>
-      <c r="F108" s="26"/>
-      <c r="G108" s="24"/>
-      <c r="H108" s="22" t="s">
-        <v>419</v>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A108" s="35"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="35"/>
+      <c r="E108" s="36"/>
+      <c r="F108" s="38"/>
+      <c r="G108" s="35"/>
+      <c r="H108" s="37" t="s">
+        <v>399</v>
       </c>
       <c r="I108" s="18" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="24"/>
-      <c r="B109" s="24"/>
-      <c r="C109" s="24"/>
-      <c r="D109" s="24"/>
-      <c r="E109" s="25"/>
-      <c r="F109" s="23"/>
-      <c r="G109" s="24"/>
-      <c r="H109" s="23"/>
+        <v>392</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A109" s="35"/>
+      <c r="B109" s="35"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="35"/>
+      <c r="E109" s="36"/>
+      <c r="F109" s="39"/>
+      <c r="G109" s="35"/>
+      <c r="H109" s="39"/>
       <c r="I109" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A110" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="B110" s="24" t="s">
+      <c r="B110" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="C110" s="24" t="s">
+      <c r="C110" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D110" s="24" t="s">
-        <v>508</v>
-      </c>
-      <c r="E110" s="25" t="s">
-        <v>509</v>
-      </c>
-      <c r="F110" s="24" t="s">
-        <v>509</v>
-      </c>
-      <c r="G110" s="24"/>
+      <c r="D110" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="E110" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="F110" s="35" t="s">
+        <v>485</v>
+      </c>
+      <c r="G110" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H110" s="18" t="s">
-        <v>420</v>
+        <v>515</v>
       </c>
       <c r="I110" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="24"/>
-      <c r="B111" s="24"/>
-      <c r="C111" s="24"/>
-      <c r="D111" s="24"/>
-      <c r="E111" s="25"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="24"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A111" s="35"/>
+      <c r="B111" s="35"/>
+      <c r="C111" s="35"/>
+      <c r="D111" s="35"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="35"/>
+      <c r="G111" s="35"/>
       <c r="H111" s="18" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="I111" s="18" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="24"/>
-      <c r="B112" s="24"/>
-      <c r="C112" s="24"/>
-      <c r="D112" s="24"/>
-      <c r="E112" s="25"/>
-      <c r="F112" s="24"/>
-      <c r="G112" s="24"/>
+        <v>345</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A112" s="35"/>
+      <c r="B112" s="35"/>
+      <c r="C112" s="35"/>
+      <c r="D112" s="35"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="35"/>
+      <c r="G112" s="35"/>
       <c r="H112" s="18" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="I112" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="24"/>
-      <c r="B113" s="24"/>
-      <c r="C113" s="24"/>
-      <c r="D113" s="24"/>
-      <c r="E113" s="25"/>
-      <c r="F113" s="24"/>
-      <c r="G113" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A113" s="35"/>
+      <c r="B113" s="35"/>
+      <c r="C113" s="35"/>
+      <c r="D113" s="35"/>
+      <c r="E113" s="36"/>
+      <c r="F113" s="35"/>
+      <c r="G113" s="35"/>
       <c r="H113" s="18"/>
       <c r="I113" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A114" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="B114" s="24" t="s">
+      <c r="B114" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="C114" s="24" t="s">
+      <c r="C114" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D114" s="24" t="s">
-        <v>514</v>
-      </c>
-      <c r="E114" s="25" t="s">
-        <v>510</v>
-      </c>
-      <c r="F114" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="G114" s="24"/>
+      <c r="D114" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="E114" s="36" t="s">
+        <v>486</v>
+      </c>
+      <c r="F114" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="G114" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H114" s="18" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="I114" s="18" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="24"/>
-      <c r="B115" s="24"/>
-      <c r="C115" s="24"/>
-      <c r="D115" s="24"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="26"/>
-      <c r="G115" s="24"/>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A115" s="35"/>
+      <c r="B115" s="35"/>
+      <c r="C115" s="35"/>
+      <c r="D115" s="35"/>
+      <c r="E115" s="36"/>
+      <c r="F115" s="38"/>
+      <c r="G115" s="35"/>
       <c r="H115" s="18" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="I115" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="24"/>
-      <c r="B116" s="24"/>
-      <c r="C116" s="24"/>
-      <c r="D116" s="24"/>
-      <c r="E116" s="25"/>
-      <c r="F116" s="26"/>
-      <c r="G116" s="24"/>
+    <row r="116" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A116" s="35"/>
+      <c r="B116" s="35"/>
+      <c r="C116" s="35"/>
+      <c r="D116" s="35"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="38"/>
+      <c r="G116" s="35"/>
       <c r="H116" s="18" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="I116" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="24"/>
-      <c r="B117" s="24"/>
-      <c r="C117" s="24"/>
-      <c r="D117" s="24"/>
-      <c r="E117" s="25"/>
-      <c r="F117" s="23"/>
-      <c r="G117" s="24"/>
+    <row r="117" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A117" s="35"/>
+      <c r="B117" s="35"/>
+      <c r="C117" s="35"/>
+      <c r="D117" s="35"/>
+      <c r="E117" s="36"/>
+      <c r="F117" s="39"/>
+      <c r="G117" s="35"/>
       <c r="H117" s="18"/>
       <c r="I117" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A118" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="C118" s="24" t="s">
+      <c r="C118" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="D118" s="24" t="s">
-        <v>511</v>
-      </c>
-      <c r="E118" s="25" t="s">
-        <v>512</v>
-      </c>
-      <c r="F118" s="22" t="s">
-        <v>512</v>
-      </c>
-      <c r="G118" s="24"/>
+      <c r="D118" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="E118" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="F118" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="G118" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H118" s="18" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="24"/>
-      <c r="B119" s="24"/>
-      <c r="C119" s="24"/>
-      <c r="D119" s="24"/>
-      <c r="E119" s="25"/>
-      <c r="F119" s="26"/>
-      <c r="G119" s="24"/>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A119" s="35"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="35"/>
+      <c r="E119" s="36"/>
+      <c r="F119" s="38"/>
+      <c r="G119" s="35"/>
       <c r="H119" s="18" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="I119" s="18" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="24"/>
-      <c r="B120" s="24"/>
-      <c r="C120" s="24"/>
-      <c r="D120" s="24"/>
-      <c r="E120" s="25"/>
-      <c r="F120" s="26"/>
-      <c r="G120" s="24"/>
+    <row r="120" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A120" s="35"/>
+      <c r="B120" s="35"/>
+      <c r="C120" s="35"/>
+      <c r="D120" s="35"/>
+      <c r="E120" s="36"/>
+      <c r="F120" s="38"/>
+      <c r="G120" s="35"/>
       <c r="H120" s="18" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
       <c r="I120" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="24"/>
-      <c r="B121" s="24"/>
-      <c r="C121" s="24"/>
-      <c r="D121" s="24"/>
-      <c r="E121" s="25"/>
-      <c r="F121" s="23"/>
-      <c r="G121" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A121" s="35"/>
+      <c r="B121" s="35"/>
+      <c r="C121" s="35"/>
+      <c r="D121" s="35"/>
+      <c r="E121" s="36"/>
+      <c r="F121" s="39"/>
+      <c r="G121" s="35"/>
       <c r="H121" s="18"/>
       <c r="I121" s="18" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="24" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A122" s="35" t="s">
         <v>289</v>
       </c>
-      <c r="B122" s="24" t="s">
+      <c r="B122" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="C122" s="24" t="s">
+      <c r="C122" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D122" s="24" t="s">
-        <v>513</v>
-      </c>
-      <c r="E122" s="25" t="s">
+      <c r="D122" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="E122" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="F122" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="G122" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H122" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="F122" s="22" t="s">
-        <v>515</v>
-      </c>
-      <c r="G122" s="24"/>
-      <c r="H122" s="18" t="s">
-        <v>428</v>
-      </c>
       <c r="I122" s="18" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="24"/>
-      <c r="B123" s="24"/>
-      <c r="C123" s="24"/>
-      <c r="D123" s="24"/>
-      <c r="E123" s="25"/>
-      <c r="F123" s="26"/>
-      <c r="G123" s="24"/>
+        <v>372</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A123" s="35"/>
+      <c r="B123" s="35"/>
+      <c r="C123" s="35"/>
+      <c r="D123" s="35"/>
+      <c r="E123" s="36"/>
+      <c r="F123" s="38"/>
+      <c r="G123" s="35"/>
       <c r="H123" s="18" t="s">
-        <v>429</v>
+        <v>407</v>
       </c>
       <c r="I123" s="18" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="24"/>
-      <c r="B124" s="24"/>
-      <c r="C124" s="24"/>
-      <c r="D124" s="24"/>
-      <c r="E124" s="25"/>
-      <c r="F124" s="26"/>
-      <c r="G124" s="24"/>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A124" s="35"/>
+      <c r="B124" s="35"/>
+      <c r="C124" s="35"/>
+      <c r="D124" s="35"/>
+      <c r="E124" s="36"/>
+      <c r="F124" s="38"/>
+      <c r="G124" s="35"/>
       <c r="H124" s="18" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="I124" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="24"/>
-      <c r="B125" s="24"/>
-      <c r="C125" s="24"/>
-      <c r="D125" s="24"/>
-      <c r="E125" s="25"/>
-      <c r="F125" s="23"/>
-      <c r="G125" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A125" s="35"/>
+      <c r="B125" s="35"/>
+      <c r="C125" s="35"/>
+      <c r="D125" s="35"/>
+      <c r="E125" s="36"/>
+      <c r="F125" s="39"/>
+      <c r="G125" s="35"/>
       <c r="H125" s="18"/>
       <c r="I125" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="126" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A126" s="35" t="s">
         <v>290</v>
       </c>
-      <c r="B126" s="24" t="s">
+      <c r="B126" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="C126" s="24" t="s">
+      <c r="C126" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="D126" s="24" t="s">
+      <c r="D126" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="E126" s="25" t="s">
+      <c r="E126" s="36" t="s">
         <v>305</v>
       </c>
-      <c r="F126" s="22" t="s">
+      <c r="F126" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="G126" s="24"/>
+      <c r="G126" s="35" t="s">
+        <v>494</v>
+      </c>
       <c r="H126" s="18" t="s">
-        <v>431</v>
+        <v>517</v>
       </c>
       <c r="I126" s="18" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="24"/>
-      <c r="B127" s="24"/>
-      <c r="C127" s="24"/>
-      <c r="D127" s="24"/>
-      <c r="E127" s="25"/>
-      <c r="F127" s="26"/>
-      <c r="G127" s="24"/>
+        <v>361</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A127" s="35"/>
+      <c r="B127" s="35"/>
+      <c r="C127" s="35"/>
+      <c r="D127" s="35"/>
+      <c r="E127" s="36"/>
+      <c r="F127" s="38"/>
+      <c r="G127" s="35"/>
       <c r="H127" s="18" t="s">
-        <v>432</v>
+        <v>409</v>
       </c>
       <c r="I127" s="18" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="24"/>
-      <c r="B128" s="24"/>
-      <c r="C128" s="24"/>
-      <c r="D128" s="24"/>
-      <c r="E128" s="25"/>
-      <c r="F128" s="26"/>
-      <c r="G128" s="24"/>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A128" s="35"/>
+      <c r="B128" s="35"/>
+      <c r="C128" s="35"/>
+      <c r="D128" s="35"/>
+      <c r="E128" s="36"/>
+      <c r="F128" s="38"/>
+      <c r="G128" s="35"/>
       <c r="H128" s="18" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="I128" s="18" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="24"/>
-      <c r="B129" s="24"/>
-      <c r="C129" s="24"/>
-      <c r="D129" s="24"/>
-      <c r="E129" s="25"/>
-      <c r="F129" s="23"/>
-      <c r="G129" s="24"/>
+    <row r="129" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A129" s="35"/>
+      <c r="B129" s="35"/>
+      <c r="C129" s="35"/>
+      <c r="D129" s="35"/>
+      <c r="E129" s="36"/>
+      <c r="F129" s="39"/>
+      <c r="G129" s="35"/>
       <c r="H129" s="18"/>
       <c r="I129" s="18" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A130" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="B130" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="C130" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D130" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="E130" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="F130" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="G130" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H130" s="18" t="s">
+        <v>518</v>
+      </c>
+      <c r="I130" s="18" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A131" s="35"/>
+      <c r="B131" s="35"/>
+      <c r="C131" s="35"/>
+      <c r="D131" s="35"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="35"/>
+      <c r="G131" s="35"/>
+      <c r="H131" s="18" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="24" t="s">
-        <v>291</v>
-      </c>
-      <c r="B130" s="24" t="s">
-        <v>306</v>
-      </c>
-      <c r="C130" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="D130" s="24" t="s">
-        <v>307</v>
-      </c>
-      <c r="E130" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="F130" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="G130" s="24"/>
-      <c r="H130" s="18" t="s">
-        <v>434</v>
-      </c>
-      <c r="I130" s="18" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="24"/>
-      <c r="B131" s="24"/>
-      <c r="C131" s="24"/>
-      <c r="D131" s="24"/>
-      <c r="E131" s="25"/>
-      <c r="F131" s="24"/>
-      <c r="G131" s="24"/>
-      <c r="H131" s="18" t="s">
-        <v>435</v>
-      </c>
       <c r="I131" s="18" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="24"/>
-      <c r="B132" s="24"/>
-      <c r="C132" s="24"/>
-      <c r="D132" s="24"/>
-      <c r="E132" s="25"/>
-      <c r="F132" s="24"/>
-      <c r="G132" s="24"/>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A132" s="35"/>
+      <c r="B132" s="35"/>
+      <c r="C132" s="35"/>
+      <c r="D132" s="35"/>
+      <c r="E132" s="36"/>
+      <c r="F132" s="35"/>
+      <c r="G132" s="35"/>
       <c r="H132" s="18" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="I132" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="24"/>
-      <c r="B133" s="24"/>
-      <c r="C133" s="24"/>
-      <c r="D133" s="24"/>
-      <c r="E133" s="25"/>
-      <c r="F133" s="24"/>
-      <c r="G133" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A133" s="35"/>
+      <c r="B133" s="35"/>
+      <c r="C133" s="35"/>
+      <c r="D133" s="35"/>
+      <c r="E133" s="36"/>
+      <c r="F133" s="35"/>
+      <c r="G133" s="35"/>
       <c r="H133" s="18"/>
       <c r="I133" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A134" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="B134" s="24" t="s">
+      <c r="B134" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="C134" s="24" t="s">
+      <c r="C134" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D134" s="24" t="s">
+      <c r="D134" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="E134" s="25" t="s">
+      <c r="E134" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="F134" s="24" t="s">
+      <c r="F134" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="G134" s="24"/>
+      <c r="G134" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H134" s="18" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="I134" s="18" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="24"/>
-      <c r="B135" s="24"/>
-      <c r="C135" s="24"/>
-      <c r="D135" s="24"/>
-      <c r="E135" s="25"/>
-      <c r="F135" s="24"/>
-      <c r="G135" s="24"/>
+        <v>378</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A135" s="35"/>
+      <c r="B135" s="35"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="35"/>
+      <c r="E135" s="36"/>
+      <c r="F135" s="35"/>
+      <c r="G135" s="35"/>
       <c r="H135" s="18" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="I135" s="18" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="24"/>
-      <c r="B136" s="24"/>
-      <c r="C136" s="24"/>
-      <c r="D136" s="24"/>
-      <c r="E136" s="25"/>
-      <c r="F136" s="24"/>
-      <c r="G136" s="24"/>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A136" s="35"/>
+      <c r="B136" s="35"/>
+      <c r="C136" s="35"/>
+      <c r="D136" s="35"/>
+      <c r="E136" s="36"/>
+      <c r="F136" s="35"/>
+      <c r="G136" s="35"/>
       <c r="H136" s="18" t="s">
-        <v>433</v>
+        <v>410</v>
       </c>
       <c r="I136" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="24"/>
-      <c r="B137" s="24"/>
-      <c r="C137" s="24"/>
-      <c r="D137" s="24"/>
-      <c r="E137" s="25"/>
-      <c r="F137" s="24"/>
-      <c r="G137" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A137" s="35"/>
+      <c r="B137" s="35"/>
+      <c r="C137" s="35"/>
+      <c r="D137" s="35"/>
+      <c r="E137" s="36"/>
+      <c r="F137" s="35"/>
+      <c r="G137" s="35"/>
       <c r="H137" s="18"/>
       <c r="I137" s="18" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="24" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A138" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="B138" s="24" t="s">
+      <c r="B138" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="C138" s="24" t="s">
+      <c r="C138" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="D138" s="24" t="s">
-        <v>517</v>
-      </c>
-      <c r="E138" s="25" t="s">
+      <c r="D138" s="35" t="s">
+        <v>493</v>
+      </c>
+      <c r="E138" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="F138" s="25" t="s">
+      <c r="F138" s="36" t="s">
         <v>314</v>
       </c>
-      <c r="G138" s="24"/>
+      <c r="G138" s="35" t="s">
+        <v>315</v>
+      </c>
       <c r="H138" s="18" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="I138" s="18" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="24"/>
-      <c r="B139" s="24"/>
-      <c r="C139" s="24"/>
-      <c r="D139" s="24"/>
-      <c r="E139" s="25"/>
-      <c r="F139" s="25"/>
-      <c r="G139" s="24"/>
+    <row r="139" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A139" s="35"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="35"/>
+      <c r="D139" s="35"/>
+      <c r="E139" s="36"/>
+      <c r="F139" s="36"/>
+      <c r="G139" s="35"/>
       <c r="H139" s="18" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="I139" s="18" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="24"/>
-      <c r="B140" s="24"/>
-      <c r="C140" s="24"/>
-      <c r="D140" s="24"/>
-      <c r="E140" s="25"/>
-      <c r="F140" s="25"/>
-      <c r="G140" s="24"/>
+        <v>387</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A140" s="35"/>
+      <c r="B140" s="35"/>
+      <c r="C140" s="35"/>
+      <c r="D140" s="35"/>
+      <c r="E140" s="36"/>
+      <c r="F140" s="36"/>
+      <c r="G140" s="35"/>
       <c r="H140" s="18" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="I140" s="18" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" ht="49.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="24"/>
-      <c r="B141" s="24"/>
-      <c r="C141" s="24"/>
-      <c r="D141" s="24"/>
-      <c r="E141" s="25"/>
-      <c r="F141" s="25"/>
-      <c r="G141" s="24"/>
+        <v>346</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="49.9" customHeight="1">
+      <c r="A141" s="35"/>
+      <c r="B141" s="35"/>
+      <c r="C141" s="35"/>
+      <c r="D141" s="35"/>
+      <c r="E141" s="36"/>
+      <c r="F141" s="36"/>
+      <c r="G141" s="35"/>
       <c r="H141" s="18"/>
       <c r="I141" s="18" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="247">
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="C6:C9"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="E6:E9"/>
-    <mergeCell ref="F6:F9"/>
-    <mergeCell ref="G6:G9"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="D2:D5"/>
-    <mergeCell ref="E2:E5"/>
-    <mergeCell ref="F2:F5"/>
-    <mergeCell ref="G10:G13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="C14:C17"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="E14:E17"/>
-    <mergeCell ref="F14:F17"/>
-    <mergeCell ref="G14:G17"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="C10:C13"/>
-    <mergeCell ref="D10:D13"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="B26:B29"/>
-    <mergeCell ref="C26:C29"/>
-    <mergeCell ref="D26:D29"/>
-    <mergeCell ref="E26:E29"/>
-    <mergeCell ref="F18:F21"/>
-    <mergeCell ref="G18:G21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="C22:C25"/>
-    <mergeCell ref="D22:D25"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="F22:F25"/>
-    <mergeCell ref="G22:G25"/>
-    <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="C18:C21"/>
-    <mergeCell ref="D18:D21"/>
-    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="H108:H109"/>
+    <mergeCell ref="H106:H107"/>
+    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="G118:G121"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="F138:F141"/>
+    <mergeCell ref="G138:G141"/>
+    <mergeCell ref="G134:G137"/>
+    <mergeCell ref="F134:F137"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="E130:E133"/>
+    <mergeCell ref="F130:F133"/>
+    <mergeCell ref="G130:G133"/>
+    <mergeCell ref="B126:B129"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="G126:G129"/>
+    <mergeCell ref="A138:A141"/>
+    <mergeCell ref="B138:B141"/>
+    <mergeCell ref="C138:C141"/>
+    <mergeCell ref="D138:D141"/>
+    <mergeCell ref="E138:E141"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A122:A125"/>
+    <mergeCell ref="A126:A129"/>
+    <mergeCell ref="A130:A133"/>
+    <mergeCell ref="A134:A137"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="C134:C137"/>
+    <mergeCell ref="B134:B137"/>
+    <mergeCell ref="B130:B133"/>
+    <mergeCell ref="C130:C133"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="A114:A117"/>
+    <mergeCell ref="B114:B117"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="A110:A113"/>
+    <mergeCell ref="B110:B113"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="G102:G105"/>
+    <mergeCell ref="A106:A109"/>
+    <mergeCell ref="B106:B109"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="G106:G109"/>
+    <mergeCell ref="A102:A105"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="G94:G97"/>
+    <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="G98:G101"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="B94:B97"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="A90:A93"/>
+    <mergeCell ref="B90:B93"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="A86:A89"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="F78:F81"/>
+    <mergeCell ref="G78:G81"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="A78:A81"/>
+    <mergeCell ref="B78:B81"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="E78:E81"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="G70:G73"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="C74:C77"/>
+    <mergeCell ref="D74:D77"/>
+    <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F74:F77"/>
+    <mergeCell ref="G74:G77"/>
+    <mergeCell ref="A70:A73"/>
+    <mergeCell ref="B70:B73"/>
+    <mergeCell ref="C70:C73"/>
+    <mergeCell ref="D70:D73"/>
+    <mergeCell ref="E70:E73"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="G62:G65"/>
+    <mergeCell ref="A66:A69"/>
+    <mergeCell ref="B66:B69"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="E66:E69"/>
+    <mergeCell ref="F66:F69"/>
+    <mergeCell ref="G66:G69"/>
+    <mergeCell ref="A62:A65"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="D62:D65"/>
+    <mergeCell ref="E62:E65"/>
+    <mergeCell ref="F54:F57"/>
+    <mergeCell ref="G54:G57"/>
+    <mergeCell ref="G50:G53"/>
+    <mergeCell ref="A58:A61"/>
+    <mergeCell ref="B58:B61"/>
+    <mergeCell ref="C58:C61"/>
+    <mergeCell ref="D58:D61"/>
+    <mergeCell ref="E58:E61"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="G58:G61"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="B54:B57"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="D54:D57"/>
+    <mergeCell ref="E54:E57"/>
+    <mergeCell ref="A50:A53"/>
+    <mergeCell ref="B50:B53"/>
+    <mergeCell ref="C50:C53"/>
+    <mergeCell ref="D50:D53"/>
+    <mergeCell ref="E50:E53"/>
+    <mergeCell ref="F50:F53"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="E46:E49"/>
+    <mergeCell ref="F46:F49"/>
+    <mergeCell ref="G46:G49"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="C42:C45"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="E42:E45"/>
     <mergeCell ref="G34:G37"/>
     <mergeCell ref="A38:A41"/>
     <mergeCell ref="B38:B41"/>
@@ -8679,183 +8877,52 @@
     <mergeCell ref="E34:E37"/>
     <mergeCell ref="F34:F37"/>
     <mergeCell ref="A26:A29"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="A46:A49"/>
-    <mergeCell ref="B46:B49"/>
-    <mergeCell ref="C46:C49"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="E46:E49"/>
-    <mergeCell ref="F46:F49"/>
-    <mergeCell ref="G46:G49"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="C42:C45"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F54:F57"/>
-    <mergeCell ref="G54:G57"/>
-    <mergeCell ref="G50:G53"/>
-    <mergeCell ref="A58:A61"/>
-    <mergeCell ref="B58:B61"/>
-    <mergeCell ref="C58:C61"/>
-    <mergeCell ref="D58:D61"/>
-    <mergeCell ref="E58:E61"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="B54:B57"/>
-    <mergeCell ref="C54:C57"/>
-    <mergeCell ref="D54:D57"/>
-    <mergeCell ref="E54:E57"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="B50:B53"/>
-    <mergeCell ref="C50:C53"/>
-    <mergeCell ref="D50:D53"/>
-    <mergeCell ref="E50:E53"/>
-    <mergeCell ref="F50:F53"/>
-    <mergeCell ref="F62:F65"/>
-    <mergeCell ref="G62:G65"/>
-    <mergeCell ref="A66:A69"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="E66:E69"/>
-    <mergeCell ref="F66:F69"/>
-    <mergeCell ref="G66:G69"/>
-    <mergeCell ref="A62:A65"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="E62:E65"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="G70:G73"/>
-    <mergeCell ref="A74:A77"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="C74:C77"/>
-    <mergeCell ref="D74:D77"/>
-    <mergeCell ref="E74:E77"/>
-    <mergeCell ref="F74:F77"/>
-    <mergeCell ref="G74:G77"/>
-    <mergeCell ref="A70:A73"/>
-    <mergeCell ref="B70:B73"/>
-    <mergeCell ref="C70:C73"/>
-    <mergeCell ref="D70:D73"/>
-    <mergeCell ref="E70:E73"/>
-    <mergeCell ref="F78:F81"/>
-    <mergeCell ref="G78:G81"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="A78:A81"/>
-    <mergeCell ref="B78:B81"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="E78:E81"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="G86:G89"/>
-    <mergeCell ref="A90:A93"/>
-    <mergeCell ref="B90:B93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="A86:A89"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="G94:G97"/>
-    <mergeCell ref="A98:A101"/>
-    <mergeCell ref="B98:B101"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="G98:G101"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="B94:B97"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="G102:G105"/>
-    <mergeCell ref="A106:A109"/>
-    <mergeCell ref="B106:B109"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="G106:G109"/>
-    <mergeCell ref="A102:A105"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="A114:A117"/>
-    <mergeCell ref="B114:B117"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="A110:A113"/>
-    <mergeCell ref="B110:B113"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="A138:A141"/>
-    <mergeCell ref="B138:B141"/>
-    <mergeCell ref="C138:C141"/>
-    <mergeCell ref="D138:D141"/>
-    <mergeCell ref="E138:E141"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A122:A125"/>
-    <mergeCell ref="A126:A129"/>
-    <mergeCell ref="A130:A133"/>
-    <mergeCell ref="A134:A137"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="C134:C137"/>
-    <mergeCell ref="B134:B137"/>
-    <mergeCell ref="B130:B133"/>
-    <mergeCell ref="C130:C133"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="F138:F141"/>
-    <mergeCell ref="G138:G141"/>
-    <mergeCell ref="G134:G137"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="E130:E133"/>
-    <mergeCell ref="F130:F133"/>
-    <mergeCell ref="G130:G133"/>
-    <mergeCell ref="B126:B129"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="G126:G129"/>
-    <mergeCell ref="H108:H109"/>
-    <mergeCell ref="H106:H107"/>
-    <mergeCell ref="G122:G125"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="G118:G121"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="F18:F21"/>
+    <mergeCell ref="G18:G21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="C22:C25"/>
+    <mergeCell ref="D22:D25"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="F22:F25"/>
+    <mergeCell ref="G22:G25"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="C18:C21"/>
+    <mergeCell ref="D18:D21"/>
+    <mergeCell ref="E18:E21"/>
+    <mergeCell ref="G10:G13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="C14:C17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="G14:G17"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="G2:G5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="C6:C9"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="G6:G9"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="C2:C5"/>
+    <mergeCell ref="D2:D5"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="F2:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8865,55 +8932,55 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EC46D7C-9CF9-4B40-BC6C-102302ABB52B}">
   <dimension ref="A1:A10"/>
-  <sheetFormatPr defaultRowHeight="22.15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="22.15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="97.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="22.15" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" ht="22.15" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" ht="22.15" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" ht="22.15" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" ht="22.15" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" ht="22.15" customHeight="1">
       <c r="A6" s="10"/>
     </row>
-    <row r="7" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="22.15" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="22.15" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" ht="22.15" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" ht="22.15" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -8926,890 +8993,890 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A3933E-C927-46FE-8BDE-D40A884569DF}">
   <dimension ref="A1:A213"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="162.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="11" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="12" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="13" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="13" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="13" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="13" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="11" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="12" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="13" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="13" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="13" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="14"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="12" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" s="13" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" s="13" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" s="13" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" s="13" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" s="12" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" s="13" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" s="11" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" s="13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1">
       <c r="A47" s="14"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1">
       <c r="A48" s="12" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1">
       <c r="A49" s="13" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1">
       <c r="A50" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:1">
       <c r="A51" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:1">
       <c r="A52" s="12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:1">
       <c r="A53" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:1">
       <c r="A54" s="13" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:1">
       <c r="A55" s="13" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1">
       <c r="A58" s="11" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1">
       <c r="A59" s="12" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1">
       <c r="A60" s="13" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1">
       <c r="A61" s="13" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1">
       <c r="A62" s="13" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1">
       <c r="A63" s="12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1">
       <c r="A64" s="13" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:1">
       <c r="A65" s="13" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:1">
       <c r="A66" s="13" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:1">
       <c r="A69" s="11" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:1">
       <c r="A70" s="13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:1">
       <c r="A71" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:1">
       <c r="A72" s="13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:1">
       <c r="A73" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:1">
       <c r="A74" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:1">
       <c r="A75" s="13"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:1">
       <c r="A76" s="13"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:1">
       <c r="A77" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:1">
       <c r="A78" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:1">
       <c r="A79" s="13" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:1">
       <c r="A80" s="13" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:1">
       <c r="A81" s="13" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:1">
       <c r="A82" s="13" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:1">
       <c r="A83" s="13" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:1">
       <c r="A86" s="11" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:1">
       <c r="A87" s="12" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:1">
       <c r="A88" s="13" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:1">
       <c r="A89" s="13" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:1">
       <c r="A90" s="13" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:1">
       <c r="A91" s="12" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:1">
       <c r="A92" s="13" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:1">
       <c r="A93" s="13" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:1">
       <c r="A94" s="13" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:1">
       <c r="A97" s="11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:1">
       <c r="A98" s="13" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:1">
       <c r="A99" s="13" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:1">
       <c r="A100" s="13" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:1">
       <c r="A101" s="13" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:1">
       <c r="A102" s="13"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:1">
       <c r="A103" s="13"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:1">
       <c r="A104" s="11" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:1">
       <c r="A105" s="12" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:1">
       <c r="A106" s="13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:1">
       <c r="A107" s="13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:1">
       <c r="A108" s="12" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:1">
       <c r="A109" s="13" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:1">
       <c r="A110" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1">
       <c r="A111" s="12" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1">
       <c r="A112" s="13" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:1">
       <c r="A113" s="13" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:1">
       <c r="A116" s="11" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:1">
       <c r="A117" s="13" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:1">
       <c r="A118" s="13" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:1">
       <c r="A119" s="13" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:1">
       <c r="A122" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1">
       <c r="A123" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:1">
       <c r="A124" s="13" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:1">
       <c r="A125" s="13" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:1">
       <c r="A126" s="13" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:1">
       <c r="A127" s="12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:1">
       <c r="A128" s="13" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:1">
       <c r="A129" s="13" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:1">
       <c r="A130" s="13" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:1">
       <c r="A131" s="13"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:1">
       <c r="A132" s="12"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:1">
       <c r="A133" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:1">
       <c r="A134" s="13" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:1">
       <c r="A135" s="13" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:1">
       <c r="A136" s="13" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:1">
       <c r="A137" s="13" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:1">
       <c r="A140" s="11" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:1">
       <c r="A141" s="13" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:1">
       <c r="A142" s="13" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:1">
       <c r="A143" s="13" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:1">
       <c r="A144" s="13" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1">
       <c r="A145" s="13" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1">
       <c r="A146" s="13" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:1">
       <c r="A149" s="11" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:1">
       <c r="A150" s="13" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:1">
       <c r="A151" s="13" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:1">
       <c r="A152" s="13" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:1">
       <c r="A153" s="13" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:1">
       <c r="A154" s="13" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:1">
       <c r="A155" s="13" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:1">
       <c r="A156" s="13" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:1">
       <c r="A157" s="12"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:1">
       <c r="A158" s="12"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:1">
       <c r="A159" s="11" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:1">
       <c r="A160" s="13" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:1">
       <c r="A161" s="13" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:1">
       <c r="A162" s="13" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:1">
       <c r="A163" s="13" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:1">
       <c r="A164" s="13" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:1">
       <c r="A165" s="13" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:1">
       <c r="A166" s="13" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:1">
       <c r="A169" s="11" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:1">
       <c r="A170" s="13" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:1">
       <c r="A171" s="13" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:1">
       <c r="A172" s="13" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:1">
       <c r="A173" s="13" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:1">
       <c r="A176" s="11" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:1">
       <c r="A177" s="12" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:1">
       <c r="A178" s="13" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:1">
       <c r="A179" s="13" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:1">
       <c r="A180" s="12" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:1">
       <c r="A181" s="15" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:1">
       <c r="A182" s="15" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:1">
       <c r="A183" s="12" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:1">
       <c r="A184" s="15" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:1">
       <c r="A185" s="15" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:1">
       <c r="A186" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:1">
       <c r="A187" s="12" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:1">
       <c r="A188" s="15" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:1">
       <c r="A189" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:1">
       <c r="A190" s="15" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:1">
       <c r="A193" s="11" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:1">
       <c r="A194" s="12" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:1">
       <c r="A195" s="13" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:1">
       <c r="A196" s="13" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:1">
       <c r="A197" s="14"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:1">
       <c r="A198" s="12" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:1">
       <c r="A199" s="15" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:1">
       <c r="A200" s="14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:1">
       <c r="A201" s="16" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:1">
       <c r="A202" s="14" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:1">
       <c r="A203" s="12" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="204" spans="1:1" ht="45" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:1" ht="45">
       <c r="A204" s="17" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:1">
       <c r="A207" s="11" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:1">
       <c r="A208" s="13" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:1">
       <c r="A209" s="13" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:1">
       <c r="A210" s="13" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:1">
       <c r="A211" s="13" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:1">
       <c r="A212" s="13" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:1">
       <c r="A213" s="13" t="s">
         <v>231</v>
       </c>
@@ -9822,235 +9889,235 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45713967-6DC6-49B2-93C9-D103D70C4F39}">
   <dimension ref="A1:A46"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="16.899999999999999" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1">
       <c r="A6" s="4"/>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1">
       <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1">
       <c r="A9" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1">
       <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1">
       <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1">
       <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1">
       <c r="A13" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1">
       <c r="A14" s="6" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1">
       <c r="A15" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1">
       <c r="A16" s="6" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1">
       <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1">
       <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1">
       <c r="A19" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1">
       <c r="A20" s="6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1">
       <c r="A21" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1">
       <c r="A22" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1">
       <c r="A23" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1">
       <c r="A24" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:1">
       <c r="A25" s="6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1">
       <c r="A26" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1">
       <c r="A27" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1">
       <c r="A28" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1">
       <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1">
       <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1">
       <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:1">
       <c r="A32" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1">
       <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:1">
       <c r="A34" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:1">
       <c r="A35" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:1">
       <c r="A36" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:1">
       <c r="A37" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:1">
       <c r="A38" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:1">
       <c r="A39" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:1">
       <c r="A40" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:1">
       <c r="A41" s="9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:1">
       <c r="A42" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1">
       <c r="A43" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1">
       <c r="A44" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1">
       <c r="A45" s="6" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1">
       <c r="A46" s="6" t="s">
         <v>54</v>
       </c>
@@ -10061,6 +10128,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f0057ecc-156b-4664-ad1b-735689321d85" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010008FCFADE0F48AF458F68A0FF17A5B8F1" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fdfa55b6827a632f88039e9a6686a763">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f0057ecc-156b-4664-ad1b-735689321d85" xmlns:ns4="b63e7e3f-56c9-4538-aca9-9810f3c213c6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a4a02b71840093c6b517e624f6524a7" ns3:_="" ns4:_="">
     <xsd:import namespace="f0057ecc-156b-4664-ad1b-735689321d85"/>
@@ -10293,24 +10377,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E806772B-6AE8-4D49-A5F6-9E9B43D6C82B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="b63e7e3f-56c9-4538-aca9-9810f3c213c6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="f0057ecc-156b-4664-ad1b-735689321d85"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f0057ecc-156b-4664-ad1b-735689321d85" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FABE1BF-3937-4128-A142-8C998755506E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A25DDF6-7F12-4937-BF19-7E4349AA7DAC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10329,31 +10421,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FABE1BF-3937-4128-A142-8C998755506E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E806772B-6AE8-4D49-A5F6-9E9B43D6C82B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="b63e7e3f-56c9-4538-aca9-9810f3c213c6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="f0057ecc-156b-4664-ad1b-735689321d85"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{1337832b-e06e-4e87-85f5-ecfde68f9c8e}" enabled="1" method="Standard" siteId="{44e3cf94-19c9-4e32-96c3-14f5bf01391a}" removed="0"/>
